--- a/outputs/patched_ann_grid.xlsx
+++ b/outputs/patched_ann_grid.xlsx
@@ -476,20 +476,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.030044838786125</v>
+        <v>7.008227184414864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5699188057410153</v>
+        <v>1.806422563115009</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8217577576637268</v>
+        <v>-0.2156415700912476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1325776839600701</v>
+        <v>1.880556148377381</v>
       </c>
     </row>
     <row r="3">
@@ -503,20 +503,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.169756487011909</v>
+        <v>7.337846234440804</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2988688963154904</v>
+        <v>1.245960502015729</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8220675468444825</v>
+        <v>-0.131558883190155</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1361022621213229</v>
+        <v>1.67337335093499</v>
       </c>
     </row>
     <row r="4">
@@ -530,20 +530,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.180516317486763</v>
+        <v>7.399432957172394</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6106555616509125</v>
+        <v>1.002939627174502</v>
       </c>
       <c r="F4" t="n">
-        <v>0.809390926361084</v>
+        <v>-0.3637040734291077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1535694799488645</v>
+        <v>2.157002349434029</v>
       </c>
     </row>
     <row r="5">
@@ -557,20 +557,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.251635611057281</v>
+        <v>7.512368187308311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3085381090631436</v>
+        <v>1.645555578754827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8217396140098572</v>
+        <v>-0.3288786888122558</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1397897777004473</v>
+        <v>2.076853088045143</v>
       </c>
     </row>
     <row r="6">
@@ -584,20 +584,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.263043269515038</v>
+        <v>7.526438385248184</v>
       </c>
       <c r="E6" t="n">
-        <v>1.09791865856608</v>
+        <v>0.9080439666835051</v>
       </c>
       <c r="F6" t="n">
-        <v>0.816941785812378</v>
+        <v>-0.3799163341522217</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1292142289713215</v>
+        <v>2.179657940272019</v>
       </c>
     </row>
     <row r="7">
@@ -611,20 +611,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.324565023183823</v>
+        <v>7.588866129517555</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7151312945566866</v>
+        <v>2.38422628248335</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8168110370635986</v>
+        <v>-0.1601909637451172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1501179422419455</v>
+        <v>1.702204598454322</v>
       </c>
     </row>
     <row r="8">
@@ -638,20 +638,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.339803174138069</v>
+        <v>7.686254307627678</v>
       </c>
       <c r="E8" t="n">
-        <v>1.163833207008714</v>
+        <v>1.665289206544194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.817362928390503</v>
+        <v>-0.2653233528137207</v>
       </c>
       <c r="G8" t="n">
-        <v>0.114496790453923</v>
+        <v>1.914745098252183</v>
       </c>
     </row>
     <row r="9">
@@ -665,20 +665,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.385200977325439</v>
+        <v>7.715515419840813</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6140872170894333</v>
+        <v>2.016977309233021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8078576564788819</v>
+        <v>-0.3624902844429016</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1610499067132831</v>
+        <v>2.1171832357687</v>
       </c>
     </row>
     <row r="10">
@@ -692,20 +692,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.408261343836784</v>
+        <v>7.734411805868149</v>
       </c>
       <c r="E10" t="n">
-        <v>1.143718537825476</v>
+        <v>1.830864770104565</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7960650324821472</v>
+        <v>-0.7732484936714172</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1948753050164627</v>
+        <v>2.961306847957459</v>
       </c>
     </row>
     <row r="11">
@@ -719,20 +719,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.449683964252472</v>
+        <v>7.78913751244545</v>
       </c>
       <c r="E11" t="n">
-        <v>1.022482535801115</v>
+        <v>2.292925555719514</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7846824407577515</v>
+        <v>-0.2554660558700562</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2133245118080189</v>
+        <v>1.871534421592341</v>
       </c>
     </row>
     <row r="12">
@@ -746,20 +746,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.450371727347374</v>
+        <v>7.821034267544746</v>
       </c>
       <c r="E12" t="n">
-        <v>1.200323068965804</v>
+        <v>1.917115592613151</v>
       </c>
       <c r="F12" t="n">
-        <v>0.81405588388443</v>
+        <v>-1.213700890541077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.122122961970072</v>
+        <v>3.87492543276828</v>
       </c>
     </row>
     <row r="13">
@@ -773,20 +773,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5.499716326594353</v>
+        <v>7.84952200949192</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9469411992603882</v>
+        <v>1.463320145213179</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7991051435470581</v>
+        <v>-0.9677449584007263</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1607405198499676</v>
+        <v>3.339907790674223</v>
       </c>
     </row>
     <row r="14">
@@ -800,20 +800,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.60747854411602</v>
+        <v>7.865811958909035</v>
       </c>
       <c r="E14" t="n">
-        <v>0.973496398258889</v>
+        <v>1.95313843414171</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7885964274406433</v>
+        <v>-0.3300805687904358</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1999891768523799</v>
+        <v>2.031926531673224</v>
       </c>
     </row>
     <row r="15">
@@ -827,20 +827,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.627202466130257</v>
+        <v>7.879435569047928</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9525315688504901</v>
+        <v>2.172896935367853</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7818383336067199</v>
+        <v>-0.220680820941925</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1831936299374128</v>
+        <v>1.75192636251522</v>
       </c>
     </row>
     <row r="16">
@@ -854,20 +854,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.634795799851418</v>
+        <v>7.907520532608032</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7140597124021526</v>
+        <v>2.374089320502033</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7960194706916809</v>
+        <v>-0.255685293674469</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1580053588898889</v>
+        <v>1.845304244250106</v>
       </c>
     </row>
     <row r="17">
@@ -881,20 +881,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.649815201759338</v>
+        <v>7.984851002693176</v>
       </c>
       <c r="E17" t="n">
-        <v>1.282952188429258</v>
+        <v>2.687602635802328</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8124622821807861</v>
+        <v>-0.2799176096916199</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1113631483316033</v>
+        <v>1.934921594513607</v>
       </c>
     </row>
     <row r="18">
@@ -908,20 +908,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5.704501643776894</v>
+        <v>8.037720769643784</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8047131472238193</v>
+        <v>1.760985233441941</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7824970245361328</v>
+        <v>-0.2800532817840576</v>
       </c>
       <c r="G18" t="n">
-        <v>0.219757383039444</v>
+        <v>1.882080652993529</v>
       </c>
     </row>
     <row r="19">
@@ -935,20 +935,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.716593563556671</v>
+        <v>8.144230246543884</v>
       </c>
       <c r="E19" t="n">
-        <v>1.017722275613699</v>
+        <v>1.992813032722124</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7716848731040955</v>
+        <v>-0.8433944702148437</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2349182005261947</v>
+        <v>3.023354827802414</v>
       </c>
     </row>
     <row r="20">
@@ -962,20 +962,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.729981511831284</v>
+        <v>8.188274726271629</v>
       </c>
       <c r="E20" t="n">
-        <v>1.218765296478869</v>
+        <v>3.015265801240582</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7806829214096069</v>
+        <v>-0.266542398929596</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2060934392848053</v>
+        <v>1.837251405042614</v>
       </c>
     </row>
     <row r="21">
@@ -989,20 +989,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.775860026478767</v>
+        <v>8.2733403891325</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8179184202860316</v>
+        <v>2.094498084718726</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7785289883613586</v>
+        <v>-0.2409772396087647</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1900940077303164</v>
+        <v>1.772210832294306</v>
       </c>
     </row>
     <row r="22">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.799980387091637</v>
+        <v>8.41796487569809</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7314228266697793</v>
+        <v>1.57396585382823</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7788089275360107</v>
+        <v>-0.6317244648933411</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1741990216833208</v>
+        <v>2.396187824796062</v>
       </c>
     </row>
     <row r="23">
@@ -1043,20 +1043,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.85516631603241</v>
+        <v>8.688124269247055</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8307894895080276</v>
+        <v>1.825866607384403</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7705717444419861</v>
+        <v>-0.7745539665222168</v>
       </c>
       <c r="G23" t="n">
-        <v>0.178679505705984</v>
+        <v>2.814502995860325</v>
       </c>
     </row>
     <row r="24">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5.890168473124504</v>
+        <v>8.933324366807938</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8917286706188496</v>
+        <v>1.378530018468229</v>
       </c>
       <c r="F24" t="n">
-        <v>0.809599757194519</v>
+        <v>-0.8584981203079224</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1137690965294446</v>
+        <v>2.832614430828353</v>
       </c>
     </row>
     <row r="25">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.895354151725769</v>
+        <v>9.016884565353394</v>
       </c>
       <c r="E25" t="n">
-        <v>1.14622269969245</v>
+        <v>1.429171107428052</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7533738017082214</v>
+        <v>-0.4446877717971802</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2399105303306557</v>
+        <v>2.012007396818917</v>
       </c>
     </row>
     <row r="26">
@@ -1124,20 +1124,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.906866267323494</v>
+        <v>9.078070819377899</v>
       </c>
       <c r="E26" t="n">
-        <v>1.067052670907674</v>
+        <v>1.19309542688434</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7474876403808594</v>
+        <v>-0.9348836541175842</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2674334542312435</v>
+        <v>3.072915596729692</v>
       </c>
     </row>
     <row r="27">
@@ -1151,20 +1151,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5.964661985635757</v>
+        <v>9.144393056631088</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9054972824613809</v>
+        <v>1.310089646678104</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7596075773239136</v>
+        <v>-0.5673615097999573</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2494373658911806</v>
+        <v>2.23465232941062</v>
       </c>
     </row>
     <row r="28">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5.990587547421455</v>
+        <v>9.243708103895187</v>
       </c>
       <c r="E28" t="n">
-        <v>1.282002474823882</v>
+        <v>1.73074061184955</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7959666728973389</v>
+        <v>-0.4909931302070618</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1248114982647448</v>
+        <v>2.120523371272484</v>
       </c>
     </row>
     <row r="29">
@@ -1205,20 +1205,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.037441119551659</v>
+        <v>9.417612701654434</v>
       </c>
       <c r="E29" t="n">
-        <v>1.40960936174051</v>
+        <v>1.255263256561803</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7803716778755188</v>
+        <v>-0.9089695572853088</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1745610488273315</v>
+        <v>2.927688385073365</v>
       </c>
     </row>
     <row r="30">
@@ -1232,20 +1232,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6.168215349316597</v>
+        <v>9.464593380689621</v>
       </c>
       <c r="E30" t="n">
-        <v>1.318269775589494</v>
+        <v>1.409447727430224</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7580087780952454</v>
+        <v>-1.843887364864349</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1852792875504565</v>
+        <v>4.829143679176703</v>
       </c>
     </row>
     <row r="31">
@@ -1259,20 +1259,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.198985278606415</v>
+        <v>9.670910239219666</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9156044244310665</v>
+        <v>2.115613822533694</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7748417496681214</v>
+        <v>-0.8519440770149231</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1416243539897337</v>
+        <v>2.733814552383617</v>
       </c>
     </row>
     <row r="32">
@@ -1286,20 +1286,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.218664646148682</v>
+        <v>9.7106072306633</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8401405042579183</v>
+        <v>1.71077082377206</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7516100525856018</v>
+        <v>-0.5279644966125489</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1890717087564248</v>
+        <v>1.9976620285259</v>
       </c>
     </row>
     <row r="33">
@@ -1313,20 +1313,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6.221040636301041</v>
+        <v>9.842530936002731</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5149650065747278</v>
+        <v>1.609521470667402</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7543053865432739</v>
+        <v>-0.5675844192504883</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1833333488875037</v>
+        <v>2.104281955203725</v>
       </c>
     </row>
     <row r="34">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.243505477905273</v>
+        <v>9.848518520593643</v>
       </c>
       <c r="E34" t="n">
-        <v>1.136431244384331</v>
+        <v>1.549598104799833</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7496274948120117</v>
+        <v>-0.7813469290733337</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1937451090658439</v>
+        <v>2.529315973548365</v>
       </c>
     </row>
     <row r="35">
@@ -1367,20 +1367,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.519312486052513</v>
+        <v>10.02710714936256</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9831672458224766</v>
+        <v>1.894804516463738</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7308651685714722</v>
+        <v>-0.5725799322128295</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2046328555596468</v>
+        <v>1.981502316510068</v>
       </c>
     </row>
     <row r="36">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.741749048233032</v>
+        <v>10.18515810370445</v>
       </c>
       <c r="E36" t="n">
-        <v>1.138956746525674</v>
+        <v>2.348058508184425</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7093704462051391</v>
+        <v>-0.813540780544281</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1798054577525373</v>
+        <v>2.444120481049772</v>
       </c>
     </row>
     <row r="37">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.005861699581146</v>
+        <v>10.19541397690773</v>
       </c>
       <c r="E37" t="n">
-        <v>1.066913785038853</v>
+        <v>1.627973342426152</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7118112206459045</v>
+        <v>-1.376514148712158</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2225529453804251</v>
+        <v>3.678352746850014</v>
       </c>
     </row>
     <row r="38">
@@ -1448,20 +1448,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7.13845856487751</v>
+        <v>10.28309002518654</v>
       </c>
       <c r="E38" t="n">
-        <v>1.399473106160495</v>
+        <v>1.83187415696546</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6319970250129699</v>
+        <v>-1.234418618679047</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4054397450417821</v>
+        <v>3.241470043185232</v>
       </c>
     </row>
     <row r="39">
@@ -1479,16 +1479,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.156457304954529</v>
+        <v>10.2946113049984</v>
       </c>
       <c r="E39" t="n">
-        <v>1.306261845558522</v>
+        <v>1.942809748318593</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7321543335914612</v>
+        <v>-1.188597476482391</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1546799148750552</v>
+        <v>3.20859557484542</v>
       </c>
     </row>
     <row r="40">
@@ -1502,20 +1502,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7.444863617420197</v>
+        <v>10.57601273059845</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5965616871242526</v>
+        <v>1.406579880966722</v>
       </c>
       <c r="F40" t="n">
-        <v>0.652360987663269</v>
+        <v>-0.7789629101753235</v>
       </c>
       <c r="G40" t="n">
-        <v>0.291794024859569</v>
+        <v>2.243799375399123</v>
       </c>
     </row>
     <row r="41">
@@ -1529,20 +1529,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7.676726207137108</v>
+        <v>11.14305764436722</v>
       </c>
       <c r="E41" t="n">
-        <v>1.159960836172227</v>
+        <v>1.751482974199109</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6562538027763367</v>
+        <v>-1.305165100097656</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2816904916515438</v>
+        <v>3.272246188439803</v>
       </c>
     </row>
     <row r="42">
@@ -1560,16 +1560,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.0100355297327</v>
+        <v>17.18860372900963</v>
       </c>
       <c r="E42" t="n">
-        <v>7.772000813461913</v>
+        <v>8.233551896023172</v>
       </c>
       <c r="F42" t="n">
-        <v>0.003199601173400879</v>
+        <v>-5.426932191848755</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9308203929563703</v>
+        <v>10.67137766278031</v>
       </c>
     </row>
     <row r="43">
@@ -1583,20 +1583,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.24001777172089</v>
+        <v>17.23955288529396</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400350787638883</v>
+        <v>8.131652819870324</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1628199338912964</v>
+        <v>-5.41562077999115</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8390368933908873</v>
+        <v>10.66179200572855</v>
       </c>
     </row>
     <row r="44">
@@ -1610,20 +1610,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.86150738596916</v>
+        <v>17.35401943325996</v>
       </c>
       <c r="E44" t="n">
-        <v>3.879324880890826</v>
+        <v>7.976591336839622</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3846537351608276</v>
+        <v>-5.465903425216675</v>
       </c>
       <c r="G44" t="n">
-        <v>0.637189469632072</v>
+        <v>10.7022298435603</v>
       </c>
     </row>
     <row r="45">
@@ -1637,20 +1637,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17.86970168352127</v>
+        <v>18.29918950796127</v>
       </c>
       <c r="E45" t="n">
-        <v>3.855841043545217</v>
+        <v>6.987982159136772</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3876621246337891</v>
+        <v>-5.569554424285888</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6441275449746704</v>
+        <v>10.58795737482569</v>
       </c>
     </row>
     <row r="46">
@@ -1664,20 +1664,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.87638887763023</v>
+        <v>18.30623969435692</v>
       </c>
       <c r="E46" t="n">
-        <v>3.87051551757045</v>
+        <v>7.030678089499679</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3846049070358276</v>
+        <v>-5.556888079643249</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6453083578177513</v>
+        <v>10.55514960672071</v>
       </c>
     </row>
     <row r="47">
@@ -1691,20 +1691,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17.91628882288933</v>
+        <v>18.30971717834473</v>
       </c>
       <c r="E47" t="n">
-        <v>3.950985813769869</v>
+        <v>7.013897107550881</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.376203203201294</v>
+        <v>-5.573478150367737</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6464124904480831</v>
+        <v>10.59082280931892</v>
       </c>
     </row>
     <row r="48">
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17.9220025241375</v>
+        <v>18.31197530031204</v>
       </c>
       <c r="E48" t="n">
-        <v>3.969094870464817</v>
+        <v>7.022336989938021</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3747264862060547</v>
+        <v>-5.558951497077942</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6445279416556751</v>
+        <v>10.55984028950115</v>
       </c>
     </row>
     <row r="49">
@@ -1745,20 +1745,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.92684331536293</v>
+        <v>18.3784893155098</v>
       </c>
       <c r="E49" t="n">
-        <v>3.979488268726511</v>
+        <v>7.011115141839738</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3725012540817261</v>
+        <v>-5.577347135543823</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6472104136118103</v>
+        <v>10.57748395040206</v>
       </c>
     </row>
     <row r="50">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.98869907855988</v>
+        <v>18.38845387101173</v>
       </c>
       <c r="E50" t="n">
-        <v>4.290402076441463</v>
+        <v>7.019450114568567</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3544872045516968</v>
+        <v>-5.578357219696045</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6599885458312995</v>
+        <v>10.5776714808141</v>
       </c>
     </row>
     <row r="51">
@@ -1799,20 +1799,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18.01492422819138</v>
+        <v>18.39205324649811</v>
       </c>
       <c r="E51" t="n">
-        <v>4.406625535085658</v>
+        <v>7.007095725833745</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3516219854354858</v>
+        <v>-5.572254025936127</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6509665261745853</v>
+        <v>10.56483116188875</v>
       </c>
     </row>
   </sheetData>
